--- a/excel-files/TAGUIG_PATEROS/COMEMBO ES.xlsx
+++ b/excel-files/TAGUIG_PATEROS/COMEMBO ES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="643" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC7CB5D-AE64-49A4-85ED-801A15454019}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB9D8642-9C31-46B1-ABB1-26107FD8512B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>Arts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -5774,7 +5777,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2024</v>
       </c>
-      <c r="K3" s="34"/>
+      <c r="K3" s="34">
+        <v>0</v>
+      </c>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
@@ -5789,7 +5794,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2024</v>
       </c>
-      <c r="Q3" s="34"/>
+      <c r="Q3" s="34">
+        <v>0</v>
+      </c>
       <c r="R3" s="32"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34">
@@ -5804,7 +5811,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2024</v>
       </c>
-      <c r="W3" s="34"/>
+      <c r="W3" s="34">
+        <v>0</v>
+      </c>
       <c r="X3" s="32"/>
       <c r="Y3" s="34"/>
       <c r="Z3" s="34">
@@ -5859,7 +5868,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -5874,7 +5885,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -5889,7 +5902,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -5932,7 +5947,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -5947,7 +5964,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -5962,7 +5981,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -6005,7 +6026,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -6020,7 +6043,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -6035,7 +6060,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -6078,7 +6105,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -6093,7 +6122,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -6108,7 +6139,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -6151,7 +6184,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -6166,7 +6201,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -6181,7 +6218,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -6224,7 +6263,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -6239,7 +6280,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -6254,7 +6297,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -6297,7 +6342,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
@@ -6312,7 +6359,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q11" s="5"/>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
@@ -6327,7 +6376,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W11" s="5"/>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
@@ -6370,7 +6421,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -6385,7 +6438,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -6400,7 +6455,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>1824</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -6683,12 +6740,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2504</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+      <c r="K17" s="5">
+        <v>314</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>2504</v>
+        <v>2190</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6837,12 +6900,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2504</v>
       </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="5"/>
+      <c r="K19" s="5">
+        <v>314</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>2504</v>
+        <v>2190</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -7279,13 +7348,17 @@
         <v>2424</v>
       </c>
       <c r="E26" s="5">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>2424</v>
+        <v>2165</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="3"/>
@@ -7352,13 +7425,17 @@
         <v>2424</v>
       </c>
       <c r="E27" s="5">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
-        <v>2424</v>
+        <v>2165</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="3"/>
@@ -7425,13 +7502,17 @@
         <v>2424</v>
       </c>
       <c r="E28" s="5">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>2424</v>
+        <v>2165</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="3"/>
@@ -7498,13 +7579,17 @@
         <v>2424</v>
       </c>
       <c r="E29" s="5">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>2424</v>
+        <v>2165</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -8426,12 +8511,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+      <c r="K43" s="5">
+        <v>337</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>2664</v>
+        <v>2327</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8580,12 +8671,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2664</v>
       </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="5"/>
+      <c r="K45" s="5">
+        <v>337</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>2664</v>
+        <v>2327</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -17957,7 +18054,7 @@
         <v>2184</v>
       </c>
       <c r="E56" s="5">
-        <v>770</v>
+        <v>980</v>
       </c>
       <c r="F56" s="1">
         <v>2025</v>
@@ -17967,7 +18064,7 @@
       </c>
       <c r="H56" s="5">
         <f t="shared" si="0"/>
-        <v>1414</v>
+        <v>1204</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="1"/>
@@ -18137,7 +18234,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C58" s="1">
         <v>273</v>
